--- a/data/trans_camb/IP16_n_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16_n_R2-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-30,13; 10,07</t>
+          <t>-30,43; 9,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-48,42; -14,97</t>
+          <t>-46,18; -14,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,2; 26,92</t>
+          <t>-15,75; 26,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-35,97; -1,62</t>
+          <t>-35,21; 2,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-40,4; -4,21</t>
+          <t>-40,32; -2,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-28,43; 11,17</t>
+          <t>-29,13; 12,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-28,74; -1,92</t>
+          <t>-27,59; -0,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-37,56; -14,17</t>
+          <t>-37,74; -14,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,46; 11,88</t>
+          <t>-17,42; 10,86</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-66,17; 40,19</t>
+          <t>-64,48; 41,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -40,75</t>
+          <t>-94,95; -42,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-36,67; 106,11</t>
+          <t>-35,18; 99,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-78,74; 2,14</t>
+          <t>-77,14; 12,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-90,68; -2,51</t>
+          <t>-91,09; 6,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-62,25; 47,4</t>
+          <t>-64,89; 48,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-64,46; -5,21</t>
+          <t>-64,15; 0,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-88,19; -40,07</t>
+          <t>-88,56; -44,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-38,72; 37,88</t>
+          <t>-40,54; 35,47</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-40,95; -10,9</t>
+          <t>-38,84; -10,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-36,96; -7,48</t>
+          <t>-36,92; -8,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-25,26; 9,26</t>
+          <t>-26,6; 8,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-32,5; -4,84</t>
+          <t>-33,09; -4,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-31,81; -4,93</t>
+          <t>-30,48; -3,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,34; 18,7</t>
+          <t>-11,04; 19,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-31,8; -10,72</t>
+          <t>-32,54; -12,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-30,04; -10,66</t>
+          <t>-30,01; -10,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 9,63</t>
+          <t>-13,96; 8,99</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-85,61; -32,27</t>
+          <t>-85,11; -33,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-77,6; -21,62</t>
+          <t>-78,42; -25,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-52,63; 29,52</t>
+          <t>-58,28; 29,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-85,51; -11,92</t>
+          <t>-85,88; -12,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-83,97; -13,51</t>
+          <t>-80,75; -10,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,66; 91,79</t>
+          <t>-30,13; 88,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-80,4; -36,72</t>
+          <t>-80,03; -40,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-74,43; -34,3</t>
+          <t>-74,25; -33,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-34,13; 33,6</t>
+          <t>-34,82; 30,7</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-31,02; 3,46</t>
+          <t>-31,89; 3,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-37,56; -4,35</t>
+          <t>-38,78; -5,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-38,72; 5,44</t>
+          <t>-36,83; 7,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-53,55; -23,38</t>
+          <t>-54,24; -23,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-41,92; -6,47</t>
+          <t>-44,2; -6,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-31,7; 6,16</t>
+          <t>-30,56; 5,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-39,16; -15,66</t>
+          <t>-38,91; -16,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-35,71; -10,63</t>
+          <t>-36,19; -11,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-29,99; -0,23</t>
+          <t>-31,51; -1,35</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-73,42; 28,8</t>
+          <t>-74,39; 18,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-90,09; -10,41</t>
+          <t>-91,23; -18,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-79,8; 21,44</t>
+          <t>-78,54; 30,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-93,53; -55,03</t>
+          <t>-93,81; -55,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-75,95; -13,14</t>
+          <t>-79,16; -13,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-57,1; 16,46</t>
+          <t>-56,08; 16,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-82,79; -45,25</t>
+          <t>-81,71; -44,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-75,39; -28,56</t>
+          <t>-76,34; -32,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-65,28; -2,23</t>
+          <t>-68,78; -5,05</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-47,44; -9,62</t>
+          <t>-46,38; -7,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-52,13; -10,13</t>
+          <t>-49,46; -10,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-33,55; 12,27</t>
+          <t>-31,66; 10,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-44,64; -13,33</t>
+          <t>-44,97; -14,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-52,99; -23,78</t>
+          <t>-52,83; -23,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-25,14; 11,49</t>
+          <t>-27,11; 10,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-41,62; -17,55</t>
+          <t>-41,39; -17,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-46,32; -22,52</t>
+          <t>-45,65; -22,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-22,31; 5,54</t>
+          <t>-22,4; 6,27</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-83,74; -28,35</t>
+          <t>-83,98; -25,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-89,27; -30,52</t>
+          <t>-89,23; -33,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-56,37; 40,21</t>
+          <t>-55,53; 34,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-83,42; -33,95</t>
+          <t>-82,99; -36,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -60,18</t>
+          <t>-95,78; -57,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-48,39; 34,73</t>
+          <t>-50,99; 27,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-78,71; -45,52</t>
+          <t>-79,05; -43,62</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-89,24; -57,92</t>
+          <t>-90,3; -61,48</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-43,74; 14,87</t>
+          <t>-43,88; 16,81</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-28,63; -10,7</t>
+          <t>-29,14; -12,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-34,38; -17,62</t>
+          <t>-33,92; -17,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-24,25; 0,87</t>
+          <t>-22,94; 0,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-34,67; -18,4</t>
+          <t>-34,22; -18,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-34,3; -17,67</t>
+          <t>-33,04; -17,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-15,41; 3,21</t>
+          <t>-14,84; 3,11</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-29,05; -17,3</t>
+          <t>-29,36; -16,78</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-31,7; -20,09</t>
+          <t>-31,74; -20,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-16,51; -1,25</t>
+          <t>-18,09; -1,19</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-66,58; -32,2</t>
+          <t>-67,33; -34,64</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-78,25; -50,6</t>
+          <t>-79,05; -52,49</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-57,26; 2,23</t>
+          <t>-55,0; 2,17</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-77,79; -51,18</t>
+          <t>-76,48; -50,67</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-76,94; -47,28</t>
+          <t>-76,58; -48,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-34,54; 8,91</t>
+          <t>-33,44; 9,03</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-69,38; -47,67</t>
+          <t>-69,16; -48,71</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-75,28; -55,25</t>
+          <t>-75,02; -56,05</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-39,98; -4,15</t>
+          <t>-41,98; -3,37</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16_n_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16_n_R2-Habitat-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumen más de dos medicamentos</t>
+          <t>Menores que consumieron más de dos medicamentos en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-18,0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-23,46</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-8,7</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-10,71</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-30,08</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4,05</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-18,0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-23,46</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-9,92</t>
+          <t>5,53</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-3,21</t>
+          <t>-1,36</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-30,43; 9,24</t>
+          <t>-35,07; 2,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-46,18; -14,49</t>
+          <t>-40,13; -5,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,75; 26,22</t>
+          <t>-29,42; 13,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-35,21; 2,27</t>
+          <t>-31,01; 9,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-40,32; -2,42</t>
+          <t>-47,39; -14,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-29,13; 12,1</t>
+          <t>-16,65; 25,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-27,59; -0,25</t>
+          <t>-27,7; -0,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-37,74; -14,36</t>
+          <t>-38,75; -13,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-17,42; 10,86</t>
+          <t>-15,08; 14,4</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-49,16%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-64,05%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-23,75%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-28,6%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-80,36%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>10,82%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-49,16%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-64,05%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-27,08%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-8,67%</t>
+          <t>-3,68%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-64,48; 41,54</t>
+          <t>-77,46; 13,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-94,95; -42,8</t>
+          <t>-90,48; -8,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-35,18; 99,34</t>
+          <t>-65,11; 49,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-77,14; 12,31</t>
+          <t>-67,83; 34,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-91,09; 6,23</t>
+          <t>-95,06; -43,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-64,89; 48,85</t>
+          <t>-34,1; 94,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-64,15; 0,4</t>
+          <t>-63,84; -3,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-88,56; -44,33</t>
+          <t>-87,91; -42,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-40,54; 35,47</t>
+          <t>-35,2; 49,51</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-18,54</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-17,36</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4,95</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-26,01</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-23,14</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-7,96</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-18,54</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-17,36</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,04</t>
+          <t>-4,42</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,7</t>
+          <t>0,3</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-38,84; -10,81</t>
+          <t>-32,77; -4,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-36,92; -8,65</t>
+          <t>-31,93; -3,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-26,6; 8,74</t>
+          <t>-10,63; 21,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-33,09; -4,46</t>
+          <t>-40,38; -12,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-30,48; -3,13</t>
+          <t>-37,42; -9,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 19,03</t>
+          <t>-18,76; 13,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-32,54; -12,53</t>
+          <t>-32,35; -12,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-30,01; -10,35</t>
+          <t>-29,87; -11,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-13,96; 8,99</t>
+          <t>-10,92; 12,3</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-61,53%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-57,62%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16,42%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-66,63%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-59,27%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-20,39%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-61,53%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-57,62%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>-11,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-4,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-85,11; -33,42</t>
+          <t>-85,33; -11,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-78,42; -25,01</t>
+          <t>-81,69; -8,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-58,28; 29,24</t>
+          <t>-30,38; 93,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-85,88; -12,9</t>
+          <t>-85,35; -30,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-80,75; -10,58</t>
+          <t>-79,69; -28,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,13; 88,25</t>
+          <t>-42,16; 41,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-80,03; -40,68</t>
+          <t>-81,05; -39,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-74,25; -33,51</t>
+          <t>-75,26; -37,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-34,82; 30,7</t>
+          <t>-27,56; 42,47</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-38,24</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-23,74</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-14,12</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-13,86</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-21,03</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-11,68</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-38,24</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-23,74</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-13,19</t>
+          <t>-1,33</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-14,73</t>
+          <t>-8,97</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-31,89; 3,01</t>
+          <t>-52,2; -21,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-38,78; -5,88</t>
+          <t>-38,7; -4,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-36,83; 7,32</t>
+          <t>-32,88; 6,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-54,24; -23,24</t>
+          <t>-30,13; 3,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-44,2; -6,68</t>
+          <t>-38,08; -4,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-30,56; 5,54</t>
+          <t>-19,73; 15,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-38,91; -16,42</t>
+          <t>-39,82; -15,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-36,19; -11,02</t>
+          <t>-36,43; -10,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-31,51; -1,35</t>
+          <t>-21,02; 3,69</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-80,88%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-50,21%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-29,86%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-43,33%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-65,74%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-36,52%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-80,88%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-50,21%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-27,89%</t>
+          <t>-4,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-36,03%</t>
+          <t>-21,92%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-74,39; 18,25</t>
+          <t>-92,86; -53,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-91,23; -18,08</t>
+          <t>-72,62; -7,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-78,54; 30,49</t>
+          <t>-58,08; 18,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-93,81; -55,88</t>
+          <t>-72,66; 16,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-79,16; -13,44</t>
+          <t>-88,64; -8,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-56,08; 16,84</t>
+          <t>-45,72; 70,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-81,71; -44,68</t>
+          <t>-82,85; -45,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-76,34; -32,41</t>
+          <t>-76,46; -27,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-68,78; -5,05</t>
+          <t>-45,52; 11,79</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-29,84</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-38,93</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-7,83</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-28,18</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-30,81</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-9,68</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-29,84</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-38,93</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-8,34</t>
+          <t>-9,76</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-9,09</t>
+          <t>-8,89</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-46,38; -7,8</t>
+          <t>-44,27; -12,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-49,46; -10,65</t>
+          <t>-54,06; -23,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-31,66; 10,45</t>
+          <t>-28,48; 11,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-44,97; -14,5</t>
+          <t>-46,14; -7,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-52,83; -23,47</t>
+          <t>-50,07; -11,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-27,11; 10,51</t>
+          <t>-31,87; 10,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-41,39; -17,42</t>
+          <t>-41,29; -16,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-45,65; -22,69</t>
+          <t>-47,11; -22,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-22,4; 6,27</t>
+          <t>-24,8; 6,79</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-65,42%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-85,35%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-17,17%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-63,79%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-69,74%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-21,9%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-65,42%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-85,35%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-18,29%</t>
+          <t>-22,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-20,17%</t>
+          <t>-19,74%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-83,98; -25,9</t>
+          <t>-82,04; -34,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-89,23; -33,09</t>
+          <t>-95,77; -57,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-55,53; 34,74</t>
+          <t>-53,08; 32,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-82,99; -36,58</t>
+          <t>-82,5; -17,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-95,78; -57,41</t>
+          <t>-89,54; -30,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-50,99; 27,77</t>
+          <t>-57,94; 33,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-79,05; -43,62</t>
+          <t>-78,36; -43,82</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-90,3; -61,48</t>
+          <t>-89,31; -58,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-43,88; 16,81</t>
+          <t>-47,35; 17,89</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-26,01</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-26,0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-5,87</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-20,33</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-25,71</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-9,75</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-26,01</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-26,0</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-6,2</t>
+          <t>-3,55</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-7,99</t>
+          <t>-4,79</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-29,14; -12,02</t>
+          <t>-33,59; -17,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-33,92; -17,92</t>
+          <t>-33,68; -16,99</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-22,94; 0,87</t>
+          <t>-14,16; 4,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-34,22; -18,22</t>
+          <t>-28,62; -11,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-33,04; -17,31</t>
+          <t>-34,7; -18,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 3,11</t>
+          <t>-12,46; 5,4</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-29,36; -16,78</t>
+          <t>-29,1; -17,2</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-31,74; -20,17</t>
+          <t>-31,9; -19,75</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-18,09; -1,19</t>
+          <t>-11,18; 2,52</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-65,38%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-65,35%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-14,74%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-53,15%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-67,21%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-25,48%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-65,38%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-65,35%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-15,57%</t>
+          <t>-9,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-20,46%</t>
+          <t>-12,26%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-67,33; -34,64</t>
+          <t>-76,87; -49,48</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-79,05; -52,49</t>
+          <t>-76,87; -47,96</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-55,0; 2,17</t>
+          <t>-31,86; 12,88</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-76,48; -50,67</t>
+          <t>-66,91; -33,23</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-76,58; -48,5</t>
+          <t>-80,14; -51,99</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-33,44; 9,03</t>
+          <t>-28,72; 16,59</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-69,16; -48,71</t>
+          <t>-69,57; -48,11</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-75,02; -56,05</t>
+          <t>-75,38; -54,76</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-41,98; -3,37</t>
+          <t>-26,59; 7,69</t>
         </is>
       </c>
     </row>
